--- a/4_Editora/2024_06_Total_Editoras_Publicas_Privadas.xlsx
+++ b/4_Editora/2024_06_Total_Editoras_Publicas_Privadas.xlsx
@@ -118,7 +118,7 @@
     <t xml:space="preserve">Universidade do Porto</t>
   </si>
   <si>
-    <t xml:space="preserve">U Porto Press</t>
+    <t xml:space="preserve">U.Porto Press</t>
   </si>
   <si>
     <t xml:space="preserve">Universidade Fernando Pessoa</t>
@@ -147,7 +147,7 @@
 Autónoma de Lisboa</t>
   </si>
   <si>
-    <t xml:space="preserve">Serviços Editoriais da UAL (EDIUAL)</t>
+    <t xml:space="preserve">Serviços Editoriais da UAL (EdiUAL)</t>
   </si>
 </sst>
 </file>
@@ -381,7 +381,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50.79"/>
@@ -527,7 +527,7 @@
         <v>12</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -550,7 +550,7 @@
         <v>28</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>58</v>
+        <v>996</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -573,7 +573,7 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>399</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
